--- a/pesaje/develop/Report/Lote-Export-Pesaje-Base.xlsx
+++ b/pesaje/develop/Report/Lote-Export-Pesaje-Base.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\pesaje\develop\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CCC972-83E8-4A1A-A0C6-68823129AED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8688DC01-54C5-421C-AB06-D42E12ABFDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -96,9 +96,6 @@
     <t>CONDUCTOR</t>
   </si>
   <si>
-    <t>UNIDAD</t>
-  </si>
-  <si>
     <t>PESO BRUTO</t>
   </si>
   <si>
@@ -112,6 +109,9 @@
   </si>
   <si>
     <t>MINERSOFT SAC</t>
+  </si>
+  <si>
+    <t>SACOS SEGÚN MINERO</t>
   </si>
 </sst>
 </file>
@@ -584,10 +584,10 @@
     <col min="5" max="5" width="23.88671875" style="4" customWidth="1"/>
     <col min="6" max="6" width="28.44140625" style="4" customWidth="1"/>
     <col min="7" max="7" width="25.77734375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="28.5546875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="24.77734375" style="4" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" style="4" customWidth="1"/>
-    <col min="11" max="26" width="24.6640625" style="4" customWidth="1"/>
+    <col min="8" max="9" width="28.5546875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="24.77734375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="14.88671875" style="4" customWidth="1"/>
+    <col min="12" max="26" width="24.6640625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.3">
@@ -645,7 +645,7 @@
     </row>
     <row r="2" spans="1:51" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -655,9 +655,9 @@
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
-      <c r="J2" s="6"/>
+      <c r="J2" s="12"/>
       <c r="K2" s="6"/>
-      <c r="L2" s="5"/>
+      <c r="L2" s="6"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
@@ -708,9 +708,9 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
-      <c r="J3" s="7"/>
+      <c r="J3" s="13"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="5"/>
+      <c r="L3" s="7"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -762,7 +762,7 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="5"/>
+      <c r="K4" s="6"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -815,7 +815,8 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="9"/>
     </row>
     <row r="6" spans="1:51" ht="18" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
@@ -829,7 +830,7 @@
       <c r="G6" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:51" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
@@ -843,6 +844,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
     </row>
     <row r="8" spans="1:51" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -869,59 +871,59 @@
       <c r="H8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:51" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -932,8 +934,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
